--- a/同音字.xlsx
+++ b/同音字.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="496">
   <si>
     <t>まち</t>
   </si>
@@ -1061,6 +1061,24 @@
   </si>
   <si>
     <t>史上</t>
+  </si>
+  <si>
+    <t>せいねん</t>
+  </si>
+  <si>
+    <t>成年</t>
+  </si>
+  <si>
+    <t>青年</t>
+  </si>
+  <si>
+    <t>こうさ</t>
+  </si>
+  <si>
+    <t>考察</t>
+  </si>
+  <si>
+    <t>考査</t>
   </si>
   <si>
     <t>ひたり</t>
@@ -2561,7 +2579,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:E297"/>
+  <dimension ref="A2:E303"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="13.8888888888889" customWidth="1"/>
@@ -4033,6 +4051,32 @@
     <row r="297" spans="1:2">
       <c r="B297" t="s">
         <v>324</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" t="s">
+        <v>325</v>
+      </c>
+      <c r="B299" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="B300" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" t="s">
+        <v>328</v>
+      </c>
+      <c r="B302" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="B303" t="s">
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -4052,74 +4096,74 @@
   <sheetData>
     <row r="2" ht="18" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:2">
       <c r="A3" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B4" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:2">
       <c r="A5" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:2">
@@ -4127,104 +4171,104 @@
         <v>60</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:3">
@@ -4237,93 +4281,93 @@
     </row>
     <row r="33" ht="18" spans="1:9">
       <c r="A33" s="2" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:9">
       <c r="A34" s="2" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:9">
       <c r="A36" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:9">
       <c r="A37" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B37" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:9">
       <c r="A39" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:9">
       <c r="A40" s="2" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:9">
       <c r="A41" s="2" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:9">
       <c r="A42" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:9">
       <c r="A44" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:9">
       <c r="A45" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:9">
       <c r="A46" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:9">
@@ -4344,117 +4388,117 @@
     </row>
     <row r="51" ht="18" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:4">
       <c r="A52" s="2" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:4">
       <c r="A54" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:4">
       <c r="A55" s="2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="56" ht="18" spans="1:4">
       <c r="A56" s="2" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:4">
       <c r="A58" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:4">
       <c r="A59" s="2" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="61" ht="18" spans="1:4">
       <c r="A61" s="2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="62" ht="18" spans="1:4">
       <c r="A62" s="2" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C62" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="64" ht="18" spans="1:4">
       <c r="A64" s="2" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65" ht="18" spans="1:2">
       <c r="A65" s="2" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="67" ht="18" spans="1:2">
       <c r="A67" s="2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="68" ht="18" spans="1:2">
       <c r="A68" s="2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="69" ht="18" spans="1:2">
       <c r="A69" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>87</v>
@@ -4462,18 +4506,18 @@
     </row>
     <row r="71" ht="18" spans="1:2">
       <c r="A71" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="72" ht="18" spans="1:2">
       <c r="A72" s="2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="73" ht="18" spans="1:2">
@@ -4486,18 +4530,18 @@
     </row>
     <row r="75" ht="18" spans="1:2">
       <c r="A75" s="2" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="76" ht="18" spans="1:2">
       <c r="A76" s="2" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="78" ht="18" spans="1:2">
@@ -4518,260 +4562,260 @@
     </row>
     <row r="81" ht="18" spans="1:4">
       <c r="A81" s="2" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="82" ht="18" spans="1:4">
       <c r="A82" s="2" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="84" ht="18" spans="1:4">
       <c r="A84" s="2" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="85" ht="18" spans="1:4">
       <c r="A85" s="2" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="87" ht="18" spans="1:4">
       <c r="A87" s="2" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="88" ht="18" spans="1:4">
       <c r="A88" s="2" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="89" ht="18" spans="1:4">
       <c r="A89" s="2" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="D89" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="91" ht="18" spans="1:4">
       <c r="A91" s="2" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="92" ht="18" spans="1:4">
       <c r="A92" s="2" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="94" ht="18" spans="1:4">
       <c r="A94" s="2" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="95" ht="18" spans="1:4">
       <c r="A95" s="2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="97" ht="18" spans="1:4">
       <c r="A97" s="2" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="98" ht="18" spans="1:4">
       <c r="A98" s="2" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="100" ht="18" spans="1:4">
       <c r="A100" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="101" ht="18" spans="1:4">
       <c r="A101" s="2" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="103" ht="18" spans="1:4">
       <c r="A103" s="2" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="104" ht="18" spans="1:4">
       <c r="A104" s="2" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="106" ht="18" spans="1:4">
       <c r="A106" s="2" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="107" ht="18" spans="1:4">
       <c r="A107" s="2" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="108" ht="14.4" customHeight="1"/>
     <row r="109" ht="18" spans="1:4">
       <c r="A109" s="2" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="110" ht="18" spans="1:4">
       <c r="A110" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="112" ht="18" spans="1:4">
       <c r="A112" s="2" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="113" ht="18" spans="1:4">
       <c r="A113" s="2" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" ht="18" spans="1:4">
       <c r="A115" s="4" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" ht="18" spans="1:4">
       <c r="A116" s="4" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="118" ht="18" spans="1:4">
       <c r="A118" s="2" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="119" ht="18" spans="1:4">
       <c r="A119" s="2" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="121" ht="18" spans="1:4">
       <c r="A121" s="2" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="122" ht="18" spans="1:4">
       <c r="A122" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="124" ht="18" spans="1:4">
       <c r="A124" s="2" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="125" ht="18" spans="1:4">
       <c r="A125" s="2" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>

--- a/同音字.xlsx
+++ b/同音字.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="同音字" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="502">
   <si>
     <t>まち</t>
   </si>
@@ -1079,6 +1079,24 @@
   </si>
   <si>
     <t>考査</t>
+  </si>
+  <si>
+    <t>きょうちょう</t>
+  </si>
+  <si>
+    <t>強調</t>
+  </si>
+  <si>
+    <t>協調</t>
+  </si>
+  <si>
+    <t>しじん</t>
+  </si>
+  <si>
+    <t>私人</t>
+  </si>
+  <si>
+    <t>詩人</t>
   </si>
   <si>
     <t>ひたり</t>
@@ -2579,7 +2597,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:E303"/>
+  <dimension ref="A2:E309"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="13.8888888888889" customWidth="1"/>
@@ -4077,6 +4095,32 @@
     <row r="303" spans="1:2">
       <c r="B303" t="s">
         <v>330</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" t="s">
+        <v>331</v>
+      </c>
+      <c r="B305" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="B306" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" t="s">
+        <v>334</v>
+      </c>
+      <c r="B308" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="B309" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -4096,74 +4140,74 @@
   <sheetData>
     <row r="2" ht="18" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:2">
       <c r="A3" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B4" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:2">
       <c r="A5" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:2">
@@ -4171,104 +4215,104 @@
         <v>60</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:3">
@@ -4281,93 +4325,93 @@
     </row>
     <row r="33" ht="18" spans="1:9">
       <c r="A33" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:9">
       <c r="A34" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:9">
       <c r="A36" s="2" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:9">
       <c r="A37" s="2" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B37" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:9">
       <c r="A39" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:9">
       <c r="A40" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:9">
       <c r="A41" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:9">
       <c r="A42" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:9">
       <c r="A44" s="2" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:9">
       <c r="A45" s="2" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:9">
       <c r="A46" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:9">
@@ -4388,117 +4432,117 @@
     </row>
     <row r="51" ht="18" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:4">
       <c r="A52" s="2" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:4">
       <c r="A54" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:4">
       <c r="A55" s="2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="56" ht="18" spans="1:4">
       <c r="A56" s="2" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:4">
       <c r="A58" s="2" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:4">
       <c r="A59" s="2" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="61" ht="18" spans="1:4">
       <c r="A61" s="2" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="62" ht="18" spans="1:4">
       <c r="A62" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="C62" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="64" ht="18" spans="1:4">
       <c r="A64" s="2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="65" ht="18" spans="1:2">
       <c r="A65" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="67" ht="18" spans="1:2">
       <c r="A67" s="2" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="68" ht="18" spans="1:2">
       <c r="A68" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="69" ht="18" spans="1:2">
       <c r="A69" s="2" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>87</v>
@@ -4506,18 +4550,18 @@
     </row>
     <row r="71" ht="18" spans="1:2">
       <c r="A71" s="2" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="72" ht="18" spans="1:2">
       <c r="A72" s="2" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="73" ht="18" spans="1:2">
@@ -4530,18 +4574,18 @@
     </row>
     <row r="75" ht="18" spans="1:2">
       <c r="A75" s="2" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="76" ht="18" spans="1:2">
       <c r="A76" s="2" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="78" ht="18" spans="1:2">
@@ -4562,260 +4606,260 @@
     </row>
     <row r="81" ht="18" spans="1:4">
       <c r="A81" s="2" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="82" ht="18" spans="1:4">
       <c r="A82" s="2" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="84" ht="18" spans="1:4">
       <c r="A84" s="2" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="85" ht="18" spans="1:4">
       <c r="A85" s="2" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="87" ht="18" spans="1:4">
       <c r="A87" s="2" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
     </row>
     <row r="88" ht="18" spans="1:4">
       <c r="A88" s="2" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="89" ht="18" spans="1:4">
       <c r="A89" s="2" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="D89" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="91" ht="18" spans="1:4">
       <c r="A91" s="2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="92" ht="18" spans="1:4">
       <c r="A92" s="2" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="94" ht="18" spans="1:4">
       <c r="A94" s="2" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="95" ht="18" spans="1:4">
       <c r="A95" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="97" ht="18" spans="1:4">
       <c r="A97" s="2" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="98" ht="18" spans="1:4">
       <c r="A98" s="2" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="100" ht="18" spans="1:4">
       <c r="A100" s="2" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="101" ht="18" spans="1:4">
       <c r="A101" s="2" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="103" ht="18" spans="1:4">
       <c r="A103" s="2" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="104" ht="18" spans="1:4">
       <c r="A104" s="2" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="106" ht="18" spans="1:4">
       <c r="A106" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="107" ht="18" spans="1:4">
       <c r="A107" s="2" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="108" ht="14.4" customHeight="1"/>
     <row r="109" ht="18" spans="1:4">
       <c r="A109" s="2" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="110" ht="18" spans="1:4">
       <c r="A110" s="2" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="112" ht="18" spans="1:4">
       <c r="A112" s="2" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="113" ht="18" spans="1:4">
       <c r="A113" s="2" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" ht="18" spans="1:4">
       <c r="A115" s="4" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" ht="18" spans="1:4">
       <c r="A116" s="4" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="118" ht="18" spans="1:4">
       <c r="A118" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="119" ht="18" spans="1:4">
       <c r="A119" s="2" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="121" ht="18" spans="1:4">
       <c r="A121" s="2" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="122" ht="18" spans="1:4">
       <c r="A122" s="2" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="124" ht="18" spans="1:4">
       <c r="A124" s="2" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="125" ht="18" spans="1:4">
       <c r="A125" s="2" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>

--- a/同音字.xlsx
+++ b/同音字.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="508">
   <si>
     <t>まち</t>
   </si>
@@ -1097,6 +1097,24 @@
   </si>
   <si>
     <t>詩人</t>
+  </si>
+  <si>
+    <t>こうきょう</t>
+  </si>
+  <si>
+    <t>好況</t>
+  </si>
+  <si>
+    <t>公共</t>
+  </si>
+  <si>
+    <t>こうひょう</t>
+  </si>
+  <si>
+    <t>好評</t>
+  </si>
+  <si>
+    <t>公表</t>
   </si>
   <si>
     <t>ひたり</t>
@@ -2597,7 +2615,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:E309"/>
+  <dimension ref="A2:E315"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="13.8888888888889" customWidth="1"/>
@@ -4121,6 +4139,32 @@
     <row r="309" spans="1:2">
       <c r="B309" t="s">
         <v>336</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" t="s">
+        <v>337</v>
+      </c>
+      <c r="B311" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="B312" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" t="s">
+        <v>340</v>
+      </c>
+      <c r="B314" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="B315" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -4140,74 +4184,74 @@
   <sheetData>
     <row r="2" ht="18" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:2">
       <c r="A3" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B4" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:2">
       <c r="A5" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:2">
@@ -4215,104 +4259,104 @@
         <v>60</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:3">
@@ -4325,93 +4369,93 @@
     </row>
     <row r="33" ht="18" spans="1:9">
       <c r="A33" s="2" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:9">
       <c r="A34" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:9">
       <c r="A36" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:9">
       <c r="A37" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B37" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:9">
       <c r="A39" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:9">
       <c r="A40" s="2" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:9">
       <c r="A41" s="2" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:9">
       <c r="A42" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:9">
       <c r="A44" s="2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:9">
       <c r="A45" s="2" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:9">
       <c r="A46" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:9">
@@ -4432,117 +4476,117 @@
     </row>
     <row r="51" ht="18" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:4">
       <c r="A52" s="2" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:4">
       <c r="A54" s="2" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:4">
       <c r="A55" s="2" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="56" ht="18" spans="1:4">
       <c r="A56" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:4">
       <c r="A58" s="2" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:4">
       <c r="A59" s="2" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="61" ht="18" spans="1:4">
       <c r="A61" s="2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="62" ht="18" spans="1:4">
       <c r="A62" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C62" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="64" ht="18" spans="1:4">
       <c r="A64" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="65" ht="18" spans="1:2">
       <c r="A65" s="2" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="67" ht="18" spans="1:2">
       <c r="A67" s="2" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="68" ht="18" spans="1:2">
       <c r="A68" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="69" ht="18" spans="1:2">
       <c r="A69" s="2" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>87</v>
@@ -4550,18 +4594,18 @@
     </row>
     <row r="71" ht="18" spans="1:2">
       <c r="A71" s="2" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="72" ht="18" spans="1:2">
       <c r="A72" s="2" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="73" ht="18" spans="1:2">
@@ -4574,18 +4618,18 @@
     </row>
     <row r="75" ht="18" spans="1:2">
       <c r="A75" s="2" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="76" ht="18" spans="1:2">
       <c r="A76" s="2" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="78" ht="18" spans="1:2">
@@ -4606,260 +4650,260 @@
     </row>
     <row r="81" ht="18" spans="1:4">
       <c r="A81" s="2" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="82" ht="18" spans="1:4">
       <c r="A82" s="2" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="84" ht="18" spans="1:4">
       <c r="A84" s="2" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="85" ht="18" spans="1:4">
       <c r="A85" s="2" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="87" ht="18" spans="1:4">
       <c r="A87" s="2" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="88" ht="18" spans="1:4">
       <c r="A88" s="2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="89" ht="18" spans="1:4">
       <c r="A89" s="2" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D89" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="91" ht="18" spans="1:4">
       <c r="A91" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="92" ht="18" spans="1:4">
       <c r="A92" s="2" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="94" ht="18" spans="1:4">
       <c r="A94" s="2" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="95" ht="18" spans="1:4">
       <c r="A95" s="2" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="97" ht="18" spans="1:4">
       <c r="A97" s="2" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="98" ht="18" spans="1:4">
       <c r="A98" s="2" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="100" ht="18" spans="1:4">
       <c r="A100" s="2" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="101" ht="18" spans="1:4">
       <c r="A101" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="103" ht="18" spans="1:4">
       <c r="A103" s="2" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="104" ht="18" spans="1:4">
       <c r="A104" s="2" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="106" ht="18" spans="1:4">
       <c r="A106" s="2" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="107" ht="18" spans="1:4">
       <c r="A107" s="2" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="108" ht="14.4" customHeight="1"/>
     <row r="109" ht="18" spans="1:4">
       <c r="A109" s="2" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="110" ht="18" spans="1:4">
       <c r="A110" s="2" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="112" ht="18" spans="1:4">
       <c r="A112" s="2" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="113" ht="18" spans="1:4">
       <c r="A113" s="2" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" ht="18" spans="1:4">
       <c r="A115" s="4" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" ht="18" spans="1:4">
       <c r="A116" s="4" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="118" ht="18" spans="1:4">
       <c r="A118" s="2" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="119" ht="18" spans="1:4">
       <c r="A119" s="2" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="121" ht="18" spans="1:4">
       <c r="A121" s="2" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="122" ht="18" spans="1:4">
       <c r="A122" s="2" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
     </row>
     <row r="124" ht="18" spans="1:4">
       <c r="A124" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
     </row>
     <row r="125" ht="18" spans="1:4">
       <c r="A125" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>
